--- a/testdata_excel/test_data.xlsx
+++ b/testdata_excel/test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlaywrightPython\testdata_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934C03B4-3E2F-44AC-930A-BAF5EBE49619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025B1CAB-E0F9-480C-95BE-CE87FAF3EFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>950812424257</v>
+        <v>950812464257</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>

--- a/testdata_excel/test_data.xlsx
+++ b/testdata_excel/test_data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlaywrightPython\testdata_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025B1CAB-E0F9-480C-95BE-CE87FAF3EFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE4F6A9-1995-4FB0-959B-DC584CA6C77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>MyKadID</t>
   </si>
@@ -39,7 +40,16 @@
     <t>Lokesh</t>
   </si>
   <si>
-    <t>Krishna</t>
+    <t>Mukesh</t>
+  </si>
+  <si>
+    <t>PolicyNo</t>
+  </si>
+  <si>
+    <t>TaxID</t>
+  </si>
+  <si>
+    <t>Policy Number</t>
   </si>
 </sst>
 </file>
@@ -83,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,6 +102,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -374,43 +387,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>890215456687</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>990514455578</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>890514455577</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55AF375-3C11-40E7-98CF-5F11C3B6C475}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>950812464257</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>990514455578</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>890514455577</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>402000070735</v>
+      </c>
+      <c r="B2" s="4">
+        <v>123654789</v>
       </c>
     </row>
   </sheetData>

--- a/testdata_excel/test_data.xlsx
+++ b/testdata_excel/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlaywrightPython\testdata_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE4F6A9-1995-4FB0-959B-DC584CA6C77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47A74FA-787D-4D68-AC8D-2D66C5218FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>MyKadID</t>
   </si>
@@ -40,16 +40,13 @@
     <t>Lokesh</t>
   </si>
   <si>
-    <t>Mukesh</t>
-  </si>
-  <si>
-    <t>PolicyNo</t>
-  </si>
-  <si>
-    <t>TaxID</t>
-  </si>
-  <si>
     <t>Policy Number</t>
+  </si>
+  <si>
+    <t>Ajay</t>
+  </si>
+  <si>
+    <t>Lucky</t>
   </si>
 </sst>
 </file>
@@ -403,15 +400,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>890215456687</v>
+        <v>890215455687</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -437,27 +434,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55AF375-3C11-40E7-98CF-5F11C3B6C475}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>950416456279</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>402000070735</v>
-      </c>
-      <c r="B2" s="4">
-        <v>123654789</v>
       </c>
     </row>
   </sheetData>

--- a/testdata_excel/test_data.xlsx
+++ b/testdata_excel/test_data.xlsx
@@ -1,81 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlaywrightPython\testdata_excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47A74FA-787D-4D68-AC8D-2D66C5218FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="PA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dental" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Motor_PC" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
-  <si>
-    <t>MyKadID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Sree</t>
-  </si>
-  <si>
-    <t>Lokesh</t>
-  </si>
-  <si>
-    <t>Policy Number</t>
-  </si>
-  <si>
-    <t>Ajay</t>
-  </si>
-  <si>
-    <t>Lucky</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -90,34 +67,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -383,49 +431,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col width="20.6640625" customWidth="1" min="1" max="1"/>
+    <col width="24.44140625" customWidth="1" min="2" max="2"/>
+    <col width="23.21875" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>890215455687</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MyKadID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Policy Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>890215452677</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Jathin</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>00000402000070798</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>990514455578</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Sree</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>890514455577</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lokesh</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -433,32 +504,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55AF375-3C11-40E7-98CF-5F11C3B6C475}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col width="23.5546875" customWidth="1" min="1" max="1"/>
+    <col width="20.88671875" customWidth="1" min="2" max="2"/>
+    <col width="21.88671875" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>950416456279</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
+    <row r="1" ht="28.8" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MyKadID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Policy Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>950416456447</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Mithil</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.44140625" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="21.5546875" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>RegNo</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>MyKadID</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Policy Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>WD2504F</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>920903-12-5800</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Krishna</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/testdata_excel/test_data.xlsx
+++ b/testdata_excel/test_data.xlsx
@@ -1,49 +1,388 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlaywrightPython\testdata_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBEB418-5530-4CF2-B2E5-7BF2E3CA9168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="396" yWindow="840" windowWidth="22644" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dental" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Motor_PC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PA" sheetId="1" r:id="rId1"/>
+    <sheet name="PA_Correction" sheetId="2" r:id="rId2"/>
+    <sheet name="PA_Endo" sheetId="3" r:id="rId3"/>
+    <sheet name="Dental" sheetId="4" r:id="rId4"/>
+    <sheet name="Motor_PC" sheetId="5" r:id="rId5"/>
+    <sheet name="Motor_MC" sheetId="6" r:id="rId6"/>
+    <sheet name="Motor_CV" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="106">
+  <si>
+    <t>Policy Number</t>
+  </si>
+  <si>
+    <t>MainReason</t>
+  </si>
+  <si>
+    <t>SubReason</t>
+  </si>
+  <si>
+    <t>TaxID</t>
+  </si>
+  <si>
+    <t>NewName</t>
+  </si>
+  <si>
+    <t>00000402000071227</t>
+  </si>
+  <si>
+    <t>Correct Policyholder Details</t>
+  </si>
+  <si>
+    <t>Correct / update Tax ID</t>
+  </si>
+  <si>
+    <t>Correct Policyholder Legal Name</t>
+  </si>
+  <si>
+    <t>Krishna</t>
+  </si>
+  <si>
+    <t>MyKadID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ProductType</t>
+  </si>
+  <si>
+    <t>PA Shield</t>
+  </si>
+  <si>
+    <t>Lokesh</t>
+  </si>
+  <si>
+    <t>Personal Accident Safe</t>
+  </si>
+  <si>
+    <t>Update Insured Person Details</t>
+  </si>
+  <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Update Policyholder Details</t>
+  </si>
+  <si>
+    <t>Puri</t>
+  </si>
+  <si>
+    <t>Sree</t>
+  </si>
+  <si>
+    <t>Loki</t>
+  </si>
+  <si>
+    <t>Mukesh</t>
+  </si>
+  <si>
+    <t>Sai</t>
+  </si>
+  <si>
+    <t>RegNo</t>
+  </si>
+  <si>
+    <t>WD2504F</t>
+  </si>
+  <si>
+    <t>920903-12-5800</t>
+  </si>
+  <si>
+    <t>QMK8237</t>
+  </si>
+  <si>
+    <t>760924-13-5426</t>
+  </si>
+  <si>
+    <t>Suresh</t>
+  </si>
+  <si>
+    <t>CBP3663</t>
+  </si>
+  <si>
+    <t>710712-01-5865</t>
+  </si>
+  <si>
+    <t>Jathin</t>
+  </si>
+  <si>
+    <t>QKP4397</t>
+  </si>
+  <si>
+    <t>620406-13-5923</t>
+  </si>
+  <si>
+    <t>JHF2913</t>
+  </si>
+  <si>
+    <t>850618-01-6241</t>
+  </si>
+  <si>
+    <t>Shiva</t>
+  </si>
+  <si>
+    <t>ADG1016</t>
+  </si>
+  <si>
+    <t>611101-08-6476</t>
+  </si>
+  <si>
+    <t>JFD3126</t>
+  </si>
+  <si>
+    <t>711105-01-5497</t>
+  </si>
+  <si>
+    <t>Venkat</t>
+  </si>
+  <si>
+    <t>JMP820</t>
+  </si>
+  <si>
+    <t>800617-01-6228</t>
+  </si>
+  <si>
+    <t>Bhuvana</t>
+  </si>
+  <si>
+    <t>SAA5462M</t>
+  </si>
+  <si>
+    <t>700325-12-5133</t>
+  </si>
+  <si>
+    <t>Uma</t>
+  </si>
+  <si>
+    <t>WMY1618</t>
+  </si>
+  <si>
+    <t>931229-10-5763</t>
+  </si>
+  <si>
+    <t>JLN3133</t>
+  </si>
+  <si>
+    <t>820115-01-6322</t>
+  </si>
+  <si>
+    <t>VML1918</t>
+  </si>
+  <si>
+    <t>910119-01-6409</t>
+  </si>
+  <si>
+    <t>BNL8065</t>
+  </si>
+  <si>
+    <t>800623-03-5708</t>
+  </si>
+  <si>
+    <t>Saki</t>
+  </si>
+  <si>
+    <t>VMF1335</t>
+  </si>
+  <si>
+    <t>790620-08-6060</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>BQS5741</t>
+  </si>
+  <si>
+    <t>980720-03-6412</t>
+  </si>
+  <si>
+    <t>Prakash</t>
+  </si>
+  <si>
+    <t>VKM4162</t>
+  </si>
+  <si>
+    <t>030105-10-0559</t>
+  </si>
+  <si>
+    <t>VMB3096</t>
+  </si>
+  <si>
+    <t>050602-14-0461</t>
+  </si>
+  <si>
+    <t>JWC2377</t>
+  </si>
+  <si>
+    <t>051107-01-1093</t>
+  </si>
+  <si>
+    <t>JTD5106</t>
+  </si>
+  <si>
+    <t>660507-04-5309</t>
+  </si>
+  <si>
+    <t>TCN6958</t>
+  </si>
+  <si>
+    <t>020718-10-1635</t>
+  </si>
+  <si>
+    <t>MDF3352</t>
+  </si>
+  <si>
+    <t>820807-04-5001</t>
+  </si>
+  <si>
+    <t>DEX3435</t>
+  </si>
+  <si>
+    <t>901002-03-5054</t>
+  </si>
+  <si>
+    <t>BusinessRegNo</t>
+  </si>
+  <si>
+    <t>ApprovalType</t>
+  </si>
+  <si>
+    <t>carryingcapacity</t>
+  </si>
+  <si>
+    <t>BJK5746</t>
+  </si>
+  <si>
+    <t>SA0319122-U</t>
+  </si>
+  <si>
+    <t>Vikas</t>
+  </si>
+  <si>
+    <t>NSTP</t>
+  </si>
+  <si>
+    <t>WMA7816</t>
+  </si>
+  <si>
+    <t>PG0172795-X</t>
+  </si>
+  <si>
+    <t>Mohit</t>
+  </si>
+  <si>
+    <t>STP</t>
+  </si>
+  <si>
+    <t>DBJ1129</t>
+  </si>
+  <si>
+    <t>KT0228515-W</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>WCQ8379</t>
+  </si>
+  <si>
+    <t>851689-U</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>WKY8591</t>
+  </si>
+  <si>
+    <t>AS0302628-U</t>
+  </si>
+  <si>
+    <t>Sundar</t>
+  </si>
+  <si>
+    <t>BEP3508</t>
+  </si>
+  <si>
+    <t>SA0258926-P</t>
+  </si>
+  <si>
+    <t>Vijay</t>
+  </si>
+  <si>
+    <t>VJ2152</t>
+  </si>
+  <si>
+    <t>002306780-X</t>
+  </si>
+  <si>
+    <t>DN7848</t>
+  </si>
+  <si>
+    <t>KT0000184-M</t>
+  </si>
+  <si>
+    <t>Vara lakshmi</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -54,8 +393,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -63,109 +408,122 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -431,72 +789,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="20.6640625" customWidth="1" min="1" max="1"/>
-    <col width="24.44140625" customWidth="1" min="2" max="2"/>
-    <col width="23.21875" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" customWidth="1"/>
+    <col min="5" max="5" width="24.21875" customWidth="1"/>
+    <col min="6" max="6" width="23.21875" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MyKadID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Policy Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>890215452677</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Jathin</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>00000402000070798</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>990514455578</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Sree</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>890514455577</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lokesh</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n"/>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>990514455574</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>890514455579</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -504,45 +845,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="23.5546875" customWidth="1" min="1" max="1"/>
-    <col width="20.88671875" customWidth="1" min="2" max="2"/>
-    <col width="21.88671875" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MyKadID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Policy Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>950416456447</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Mithil</t>
-        </is>
-      </c>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8">
+        <v>123654789</v>
+      </c>
+      <c r="E2" s="13"/>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -550,58 +928,608 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="10.44140625" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="21.5546875" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>RegNo</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>MyKadID</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Policy Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>WD2504F</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>920903-12-5800</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Krishna</t>
-        </is>
-      </c>
+    <row r="1" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="18">
+        <v>402000071180</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>950416458237</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>890115456572</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>890115456573</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>820115456571</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>880115456577</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="8">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="5">
+        <v>250</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5068</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
